--- a/Residuos/A2_Structure_Lists.xlsx
+++ b/Residuos/A2_Structure_Lists.xlsx
@@ -148,28 +148,28 @@
     <t>E5_TWWTWW</t>
   </si>
   <si>
+    <t>FERT_ORG</t>
+  </si>
+  <si>
+    <t>N2O_WASTE</t>
+  </si>
+  <si>
+    <t>CO2_WASTE</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>CO2e_WASTE</t>
+  </si>
+  <si>
+    <t>HWT</t>
+  </si>
+  <si>
+    <t>CH4_WASTE</t>
+  </si>
+  <si>
     <t>WTRU</t>
-  </si>
-  <si>
-    <t>CH4_WASTE</t>
-  </si>
-  <si>
-    <t>CO2_WASTE</t>
-  </si>
-  <si>
-    <t>CO2e_WASTE</t>
-  </si>
-  <si>
-    <t>FERT_ORG</t>
-  </si>
-  <si>
-    <t>HWT</t>
-  </si>
-  <si>
-    <t>N2O_WASTE</t>
-  </si>
-  <si>
-    <t>RM</t>
   </si>
   <si>
     <t>ECU</t>
